--- a/LISTAS/ma/SOPORTE MACIZO PARA ESTANTE (PITUTO) dismay.xlsx
+++ b/LISTAS/ma/SOPORTE MACIZO PARA ESTANTE (PITUTO) dismay.xlsx
@@ -825,14 +825,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45163.6092628765</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -878,26 +874,6 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -929,7 +905,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="28" t="n">
-        <v>23.22</v>
+        <v>26.828</v>
       </c>
       <c r="E33" s="29" t="n"/>
       <c r="F33" s="29" t="n"/>
@@ -947,7 +923,7 @@
       </c>
       <c r="C34" s="25" t="n"/>
       <c r="D34" s="28" t="n">
-        <v>16.666</v>
+        <v>19.256</v>
       </c>
       <c r="E34" s="29" t="n"/>
       <c r="F34" s="29" t="n"/>
@@ -960,7 +936,6 @@
       </c>
       <c r="E35" s="31" t="n"/>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
@@ -970,13 +945,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPORTE MACIZO PARA ESTANTE (PITUTO) dismay.xlsx
+++ b/LISTAS/ma/SOPORTE MACIZO PARA ESTANTE (PITUTO) dismay.xlsx
@@ -825,7 +825,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/SOPORTE MACIZO PARA ESTANTE (PITUTO) dismay.xlsx
+++ b/LISTAS/ma/SOPORTE MACIZO PARA ESTANTE (PITUTO) dismay.xlsx
@@ -825,7 +825,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/SOPORTE MACIZO PARA ESTANTE (PITUTO) dismay.xlsx
+++ b/LISTAS/ma/SOPORTE MACIZO PARA ESTANTE (PITUTO) dismay.xlsx
@@ -825,10 +825,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45266</v>
+        <v>45233.5866315213</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -874,6 +878,26 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -905,7 +929,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="28" t="n">
-        <v>26.828</v>
+        <v>28.5</v>
       </c>
       <c r="E33" s="29" t="n"/>
       <c r="F33" s="29" t="n"/>
@@ -923,7 +947,7 @@
       </c>
       <c r="C34" s="25" t="n"/>
       <c r="D34" s="28" t="n">
-        <v>19.256</v>
+        <v>22.4</v>
       </c>
       <c r="E34" s="29" t="n"/>
       <c r="F34" s="29" t="n"/>
@@ -936,6 +960,7 @@
       </c>
       <c r="E35" s="31" t="n"/>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
@@ -945,13 +970,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPORTE MACIZO PARA ESTANTE (PITUTO) dismay.xlsx
+++ b/LISTAS/ma/SOPORTE MACIZO PARA ESTANTE (PITUTO) dismay.xlsx
@@ -825,14 +825,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45233.5866315213</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -878,26 +874,6 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -929,7 +905,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="28" t="n">
-        <v>28.5</v>
+        <v>26.828</v>
       </c>
       <c r="E33" s="29" t="n"/>
       <c r="F33" s="29" t="n"/>
@@ -947,7 +923,7 @@
       </c>
       <c r="C34" s="25" t="n"/>
       <c r="D34" s="28" t="n">
-        <v>22.4</v>
+        <v>19.256</v>
       </c>
       <c r="E34" s="29" t="n"/>
       <c r="F34" s="29" t="n"/>
@@ -960,7 +936,6 @@
       </c>
       <c r="E35" s="31" t="n"/>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
@@ -970,13 +945,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
